--- a/src/UMS_Data.xlsx
+++ b/src/UMS_Data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="173">
   <si>
     <t>Subject Code</t>
   </si>
@@ -24,357 +24,396 @@
     <t>Subject Name</t>
   </si>
   <si>
+    <t>MATH001</t>
+  </si>
+  <si>
     <t>Mathematics</t>
   </si>
   <si>
-    <t>MATH001</t>
+    <t>CS201</t>
   </si>
   <si>
     <t>Computer Science</t>
   </si>
   <si>
-    <t>CS201</t>
+    <t>ENG101</t>
   </si>
   <si>
     <t>English</t>
   </si>
   <si>
-    <t>ENG101</t>
+    <t>PHY110</t>
+  </si>
+  <si>
+    <t>Physics</t>
+  </si>
+  <si>
+    <t>CHEM200</t>
   </si>
   <si>
     <t>Chemistry</t>
   </si>
   <si>
-    <t>CHEM200</t>
-  </si>
-  <si>
-    <t>askdka</t>
+    <t>dddd</t>
+  </si>
+  <si>
+    <t>ddd</t>
+  </si>
+  <si>
+    <t>Course ID</t>
+  </si>
+  <si>
+    <t>Course Name</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>Start Time</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>Exam Date</t>
+  </si>
+  <si>
+    <t>Intro to Algebra</t>
+  </si>
+  <si>
+    <t>Dr. Euler</t>
+  </si>
+  <si>
+    <t>Room 101</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>2025-04-20T09:00</t>
+  </si>
+  <si>
+    <t>Object-Oriented Programming</t>
+  </si>
+  <si>
+    <t>Room 202</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>2025-04-22T13:00</t>
+  </si>
+  <si>
+    <t>English Literature I</t>
+  </si>
+  <si>
+    <t>Room 303</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>2025-04-25T10:30</t>
+  </si>
+  <si>
+    <t>Organic Chemistry</t>
+  </si>
+  <si>
+    <t>Dr. Curie</t>
+  </si>
+  <si>
+    <t>Lab A</t>
+  </si>
+  <si>
+    <t>2025-04-28T00:00</t>
+  </si>
+  <si>
+    <t>Advanced CS Seminar</t>
   </si>
   <si>
     <t>CXLVK</t>
   </si>
   <si>
-    <t>Physics</t>
-  </si>
-  <si>
-    <t>PHY110</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>Course ID</t>
-  </si>
-  <si>
-    <t>Course Name</t>
-  </si>
-  <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>Instructor</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>Room</t>
-  </si>
-  <si>
-    <t>Schedule</t>
-  </si>
-  <si>
-    <t>Start Time</t>
-  </si>
-  <si>
-    <t>End Time</t>
-  </si>
-  <si>
-    <t>Exam Date</t>
-  </si>
-  <si>
-    <t>Intro to Algebra</t>
-  </si>
-  <si>
-    <t>Dr. Euler</t>
-  </si>
-  <si>
-    <t>Room 101</t>
-  </si>
-  <si>
-    <t>Monday</t>
-  </si>
-  <si>
-    <t>2025-04-20T09:00</t>
-  </si>
-  <si>
-    <t>Object-Oriented Programming</t>
+    <t>Dr. Alan</t>
+  </si>
+  <si>
+    <t>Room 404</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>2025-04-30T11:00</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Course123</t>
+  </si>
+  <si>
+    <t>Thorn</t>
+  </si>
+  <si>
+    <t>2025-04-09T00:00</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Annual Tuition</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Semester</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Thesis</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>Subjects</t>
+  </si>
+  <si>
+    <t>Courses</t>
+  </si>
+  <si>
+    <t>Alice Smith</t>
+  </si>
+  <si>
+    <t>alicepass</t>
+  </si>
+  <si>
+    <t>123 Maple St</t>
+  </si>
+  <si>
+    <t>alice@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>Fall 2025</t>
+  </si>
+  <si>
+    <t>Undergraduate</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>MATH001, CHEM200</t>
+  </si>
+  <si>
+    <t>1, 4</t>
+  </si>
+  <si>
+    <t>Bob Johnson</t>
+  </si>
+  <si>
+    <t>bobpass</t>
+  </si>
+  <si>
+    <t>456 Oak Ave</t>
+  </si>
+  <si>
+    <t>bob@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>Spring 2025</t>
+  </si>
+  <si>
+    <t>Graduate</t>
+  </si>
+  <si>
+    <t>AI Research</t>
+  </si>
+  <si>
+    <t>CS201, MATH001</t>
+  </si>
+  <si>
+    <t>2, 1</t>
+  </si>
+  <si>
+    <t>Carol Williams</t>
+  </si>
+  <si>
+    <t>carolpass</t>
+  </si>
+  <si>
+    <t>789 Pine Rd</t>
+  </si>
+  <si>
+    <t>carol@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>Winter 2025</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>ENG101, CHEM200, MATH001</t>
+  </si>
+  <si>
+    <t>3, 4, 1</t>
+  </si>
+  <si>
+    <t>Lucka Racki</t>
+  </si>
+  <si>
+    <t>luckapass</t>
+  </si>
+  <si>
+    <t>321 Birch St</t>
+  </si>
+  <si>
+    <t>lucka@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>MATH001, CS201</t>
+  </si>
+  <si>
+    <t>1, 2</t>
+  </si>
+  <si>
+    <t>Huzaifa</t>
+  </si>
+  <si>
+    <t>password123</t>
+  </si>
+  <si>
+    <t>428 Searles Court</t>
+  </si>
+  <si>
+    <t>anwar@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>Winter 2024</t>
+  </si>
+  <si>
+    <t>MATH001, CS201, ENG101</t>
+  </si>
+  <si>
+    <t>Ayaan Ahmed</t>
+  </si>
+  <si>
+    <t>786 Steven Road</t>
+  </si>
+  <si>
+    <t>ayaanh@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>PH.d</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Degree</t>
+  </si>
+  <si>
+    <t>Specialty</t>
+  </si>
+  <si>
+    <t>Courses Taught</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>FAC001</t>
+  </si>
+  <si>
+    <t>PhD in Mathematics</t>
+  </si>
+  <si>
+    <t>Number Theory</t>
+  </si>
+  <si>
+    <t>leonard@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>MacNaughton 201</t>
+  </si>
+  <si>
+    <t>FAC002</t>
   </si>
   <si>
     <t>Dr. Turing</t>
   </si>
   <si>
-    <t>Room 202</t>
-  </si>
-  <si>
-    <t>Tuesday</t>
-  </si>
-  <si>
-    <t>2025-04-22T13:00</t>
-  </si>
-  <si>
-    <t>English Literature I</t>
+    <t>PhD in Computer Science</t>
+  </si>
+  <si>
+    <t>AI &amp; Logic</t>
+  </si>
+  <si>
+    <t>Object-Oriented Programming, Advanced CS Seminar</t>
+  </si>
+  <si>
+    <t>alan@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>Thornbrough 310</t>
+  </si>
+  <si>
+    <t>FAC003</t>
+  </si>
+  <si>
+    <t>PhD in Chemistry</t>
+  </si>
+  <si>
+    <t>Organic Compounds</t>
+  </si>
+  <si>
+    <t>marie@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>Chemistry 112</t>
+  </si>
+  <si>
+    <t>FAC004</t>
   </si>
   <si>
     <t>Dr. Shakespeare</t>
   </si>
   <si>
-    <t>Room 303</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
-  </si>
-  <si>
-    <t>2025-04-25T10:30</t>
-  </si>
-  <si>
-    <t>Organic Chemistry</t>
-  </si>
-  <si>
-    <t>Dr. Curie</t>
-  </si>
-  <si>
-    <t>Lab A</t>
-  </si>
-  <si>
-    <t>Thursday</t>
-  </si>
-  <si>
-    <t>2025-04-28T14:00</t>
-  </si>
-  <si>
-    <t>Advanced CS Seminar</t>
-  </si>
-  <si>
-    <t>Dr. Alan</t>
-  </si>
-  <si>
-    <t>Room 404</t>
-  </si>
-  <si>
-    <t>Friday</t>
-  </si>
-  <si>
-    <t>2025-04-30T11:00</t>
-  </si>
-  <si>
-    <t>1Hello</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Full Name</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Annual Tuition</t>
-  </si>
-  <si>
-    <t>Balance</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Semester</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Thesis</t>
-  </si>
-  <si>
-    <t>Progress</t>
-  </si>
-  <si>
-    <t>Subjects</t>
-  </si>
-  <si>
-    <t>Courses</t>
-  </si>
-  <si>
-    <t>Alice Smith</t>
-  </si>
-  <si>
-    <t>alicepass</t>
-  </si>
-  <si>
-    <t>123 Maple St</t>
-  </si>
-  <si>
-    <t>alice@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>Fall 2025</t>
-  </si>
-  <si>
-    <t>Undergraduate</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>1, 4</t>
-  </si>
-  <si>
-    <t>Bob Johnson</t>
-  </si>
-  <si>
-    <t>bobpass</t>
-  </si>
-  <si>
-    <t>456 Oak Ave</t>
-  </si>
-  <si>
-    <t>bob@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>Spring 2025</t>
-  </si>
-  <si>
-    <t>Graduate</t>
-  </si>
-  <si>
-    <t>AI Research</t>
-  </si>
-  <si>
-    <t>2, 5</t>
-  </si>
-  <si>
-    <t>Carol Williams</t>
-  </si>
-  <si>
-    <t>carolpass</t>
-  </si>
-  <si>
-    <t>789 Pine Rd</t>
-  </si>
-  <si>
-    <t>carol@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>Winter 2025</t>
-  </si>
-  <si>
-    <t>Data Science</t>
-  </si>
-  <si>
-    <t>3, 4</t>
-  </si>
-  <si>
-    <t>Lucka Racki</t>
-  </si>
-  <si>
-    <t>luckapass</t>
-  </si>
-  <si>
-    <t>321 Birch St</t>
-  </si>
-  <si>
-    <t>lucka@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>1, 2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>password123</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Degree</t>
-  </si>
-  <si>
-    <t>Specialty</t>
-  </si>
-  <si>
-    <t>Courses Taught</t>
-  </si>
-  <si>
-    <t>Office</t>
-  </si>
-  <si>
-    <t>FAC001</t>
-  </si>
-  <si>
-    <t>PhD in Mathematics</t>
-  </si>
-  <si>
-    <t>Number Theory</t>
-  </si>
-  <si>
-    <t>leonard@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>MacNaughton 201</t>
-  </si>
-  <si>
-    <t>FAC002</t>
-  </si>
-  <si>
-    <t>PhD in Computer Science</t>
-  </si>
-  <si>
-    <t>AI &amp; Logic</t>
-  </si>
-  <si>
-    <t>Object-Oriented Programming, Advanced CS Seminar</t>
-  </si>
-  <si>
-    <t>alan@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>Thornbrough 310</t>
-  </si>
-  <si>
-    <t>FAC003</t>
-  </si>
-  <si>
-    <t>PhD in Chemistry</t>
-  </si>
-  <si>
-    <t>Organic Compounds</t>
-  </si>
-  <si>
-    <t>marie@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>Chemistry 112</t>
-  </si>
-  <si>
-    <t>FAC004</t>
-  </si>
-  <si>
     <t>PhD in Literature</t>
   </si>
   <si>
@@ -399,6 +438,12 @@
     <t>Thornbrough 309</t>
   </si>
   <si>
+    <t>F0006</t>
+  </si>
+  <si>
+    <t>Intro to Algebra (Sec 1), Intro to Algebra, Object-Oriented Programming, English Literature I</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -432,7 +477,7 @@
     <t>Campus Green</t>
   </si>
   <si>
-    <t>Thu Apr 03 14:00:56 EDT 2025</t>
+    <t>Fri Apr 04 02:11:32 EDT 2025</t>
   </si>
   <si>
     <t>AI Workshop</t>
@@ -447,6 +492,9 @@
     <t>Thornbrough 210</t>
   </si>
   <si>
+    <t>, 100001</t>
+  </si>
+  <si>
     <t>Career Fair</t>
   </si>
   <si>
@@ -459,13 +507,34 @@
     <t>UC Courtyard</t>
   </si>
   <si>
-    <t>11</t>
+    <t>Event7</t>
+  </si>
+  <si>
+    <t>E007</t>
+  </si>
+  <si>
+    <t>UC</t>
+  </si>
+  <si>
+    <t>UC CLUB FAIR</t>
+  </si>
+  <si>
+    <t>UC90</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>Wed Jan 01 00:00:00 EST 2020</t>
+    <t>PROJECT DAY</t>
+  </si>
+  <si>
+    <t>CST100</t>
+  </si>
+  <si>
+    <t>Added via UI</t>
+  </si>
+  <si>
+    <t>THORN</t>
   </si>
 </sst>
 </file>
@@ -510,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -567,14 +636,6 @@
       </c>
       <c r="B7" t="s" s="0">
         <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -584,42 +645,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>15</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>16</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>0</v>
       </c>
       <c r="D1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="F1" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="H1" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="I1" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="J1" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="K1" t="s" s="0">
         <v>23</v>
-      </c>
-      <c r="K1" t="s" s="0">
-        <v>24</v>
       </c>
     </row>
     <row r="2">
@@ -627,25 +688,25 @@
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n" s="0">
         <v>50.0</v>
       </c>
       <c r="G2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s" s="0">
         <v>27</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>28</v>
       </c>
       <c r="I2" t="n" s="0">
         <v>900.0</v>
@@ -654,7 +715,7 @@
         <v>1030.0</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -662,25 +723,25 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n" s="0">
         <v>40.0</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I3" t="n" s="0">
         <v>1100.0</v>
@@ -689,7 +750,7 @@
         <v>1230.0</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -697,25 +758,25 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>30.0</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I4" t="n" s="0">
         <v>1400.0</v>
@@ -724,7 +785,7 @@
         <v>1530.0</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -732,34 +793,34 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>35.0</v>
+        <v>2.0</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>1300.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J5" t="n" s="0">
         <v>1500.0</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -767,25 +828,25 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>25.0</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I6" t="n" s="0">
         <v>1500.0</v>
@@ -794,33 +855,33 @@
         <v>1700.0</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n" s="0">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n" s="0">
         <v>50.0</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="I7" t="n" s="0">
         <v>900.0</v>
@@ -829,7 +890,42 @@
         <v>1100.0</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>51</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>1120.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>1200.0</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -839,54 +935,54 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="E1" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="F1" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="H1" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="I1" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="J1" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="K1" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="L1" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="M1" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="N1" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="O1" t="s" s="0">
         <v>65</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>66</v>
       </c>
     </row>
     <row r="2">
@@ -894,13 +990,13 @@
         <v>100001.0</v>
       </c>
       <c r="B2" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="D2" t="s" s="0">
         <v>68</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>69</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.23456789E9</v>
@@ -912,19 +1008,19 @@
         <v>2000.0</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I2" t="n" s="0">
         <v>85.0</v>
       </c>
       <c r="J2" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="K2" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="L2" t="s" s="0">
         <v>72</v>
-      </c>
-      <c r="L2" t="s" s="0">
-        <v>73</v>
       </c>
       <c r="M2" t="n" s="0">
         <v>-1.0</v>
@@ -977,10 +1073,10 @@
         <v>-1.0</v>
       </c>
       <c r="N3" t="s" s="0">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="O3" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -988,13 +1084,13 @@
         <v>100003.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>5.55666777E8</v>
@@ -1006,28 +1102,28 @@
         <v>3000.0</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I4" t="n" s="0">
         <v>88.0</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="0">
         <v>80</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M4" t="n" s="0">
         <v>-1.0</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
@@ -1035,13 +1131,13 @@
         <v>100004.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E5" t="n" s="0">
         <v>4.44555666E8</v>
@@ -1053,45 +1149,45 @@
         <v>2500.0</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I5" t="n" s="0">
         <v>75.0</v>
       </c>
       <c r="J5" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="K5" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="K5" t="s" s="0">
+      <c r="L5" t="s" s="0">
         <v>72</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>73</v>
       </c>
       <c r="M5" t="n" s="0">
         <v>-1.0</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n" s="0">
-        <v>147781.0</v>
+        <v>870003.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>1.0</v>
+        <v>6.476748616E9</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>5000.0</v>
@@ -1100,28 +1196,75 @@
         <v>0.0</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M6" t="n" s="0">
         <v>-1.0</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>73</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>901988.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>6.845789546E9</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="M7" t="n" s="0">
+        <v>-1.0</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="O7" t="s" s="0">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1131,145 +1274,168 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>126</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1279,50 +1445,50 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="F2" t="n" s="0">
         <v>100.0</v>
@@ -1331,24 +1497,24 @@
         <v>0.0</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="F3" t="n" s="0">
         <v>30.0</v>
@@ -1357,24 +1523,24 @@
         <v>15.0</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>73</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>150.0</v>
@@ -1383,24 +1549,24 @@
         <v>0.0</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F5" t="n" s="0">
         <v>11.0</v>
@@ -1409,24 +1575,24 @@
         <v>11.0</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>11.0</v>
@@ -1435,7 +1601,59 @@
         <v>11.0</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/src/UMS_Data.xlsx
+++ b/src/UMS_Data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="177">
   <si>
     <t>Subject Code</t>
   </si>
@@ -24,42 +24,36 @@
     <t>Subject Name</t>
   </si>
   <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
     <t>MATH001</t>
   </si>
   <si>
-    <t>Mathematics</t>
+    <t>Computer Science</t>
   </si>
   <si>
     <t>CS201</t>
   </si>
   <si>
-    <t>Computer Science</t>
+    <t>English</t>
   </si>
   <si>
     <t>ENG101</t>
   </si>
   <si>
-    <t>English</t>
+    <t>Physics</t>
   </si>
   <si>
     <t>PHY110</t>
   </si>
   <si>
-    <t>Physics</t>
+    <t>Chemistry</t>
   </si>
   <si>
     <t>CHEM200</t>
   </si>
   <si>
-    <t>Chemistry</t>
-  </si>
-  <si>
-    <t>dddd</t>
-  </si>
-  <si>
-    <t>ddd</t>
-  </si>
-  <si>
     <t>Course ID</t>
   </si>
   <si>
@@ -102,7 +96,7 @@
     <t>Monday</t>
   </si>
   <si>
-    <t>2025-04-20T09:00</t>
+    <t>2025-04-20T00:00</t>
   </si>
   <si>
     <t>Object-Oriented Programming</t>
@@ -171,6 +165,12 @@
     <t>2025-04-09T00:00</t>
   </si>
   <si>
+    <t>MECHANICS</t>
+  </si>
+  <si>
+    <t>THORN</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -216,16 +216,16 @@
     <t>Courses</t>
   </si>
   <si>
-    <t>Alice Smith</t>
-  </si>
-  <si>
-    <t>alicepass</t>
+    <t>Alizay Smith</t>
+  </si>
+  <si>
+    <t>smithpass</t>
   </si>
   <si>
     <t>123 Maple St</t>
   </si>
   <si>
-    <t>alice@uoguelph.ca</t>
+    <t>alizay@uoguelph.ca</t>
   </si>
   <si>
     <t>Fall 2025</t>
@@ -237,22 +237,22 @@
     <t/>
   </si>
   <si>
-    <t>MATH001, CHEM200</t>
-  </si>
-  <si>
-    <t>1, 4</t>
-  </si>
-  <si>
-    <t>Bob Johnson</t>
-  </si>
-  <si>
-    <t>bobpass</t>
+    <t>Mathematics, Chemistry</t>
+  </si>
+  <si>
+    <t>1, 4, 5</t>
+  </si>
+  <si>
+    <t>Barbra John</t>
+  </si>
+  <si>
+    <t>barpass</t>
   </si>
   <si>
     <t>456 Oak Ave</t>
   </si>
   <si>
-    <t>bob@uoguelph.ca</t>
+    <t>barbra@uoguelph.ca</t>
   </si>
   <si>
     <t>Spring 2025</t>
@@ -264,22 +264,22 @@
     <t>AI Research</t>
   </si>
   <si>
-    <t>CS201, MATH001</t>
+    <t>Computer Science, Mathematics</t>
   </si>
   <si>
     <t>2, 1</t>
   </si>
   <si>
-    <t>Carol Williams</t>
-  </si>
-  <si>
-    <t>carolpass</t>
+    <t>Farhan Khan</t>
+  </si>
+  <si>
+    <t>farpass</t>
   </si>
   <si>
     <t>789 Pine Rd</t>
   </si>
   <si>
-    <t>carol@uoguelph.ca</t>
+    <t>farhan@uoguelph.ca</t>
   </si>
   <si>
     <t>Winter 2025</t>
@@ -288,25 +288,25 @@
     <t>Data Science</t>
   </si>
   <si>
-    <t>ENG101, CHEM200, MATH001</t>
+    <t>English, Chemistry, Mathematics</t>
   </si>
   <si>
     <t>3, 4, 1</t>
   </si>
   <si>
-    <t>Lucka Racki</t>
-  </si>
-  <si>
-    <t>luckapass</t>
+    <t>Lucy Smith</t>
+  </si>
+  <si>
+    <t>lucypass</t>
   </si>
   <si>
     <t>321 Birch St</t>
   </si>
   <si>
-    <t>lucka@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>MATH001, CS201</t>
+    <t>lucy@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>Mathematics, Computer Science</t>
   </si>
   <si>
     <t>1, 2</t>
@@ -327,7 +327,7 @@
     <t>Winter 2024</t>
   </si>
   <si>
-    <t>MATH001, CS201, ENG101</t>
+    <t>Mathematics, Computer Science, English</t>
   </si>
   <si>
     <t>Ayaan Ahmed</t>
@@ -366,6 +366,9 @@
     <t>Number Theory</t>
   </si>
   <si>
+    <t>, Intro to Algebra, Object-Oriented Programming, English Literature I</t>
+  </si>
+  <si>
     <t>leonard@uoguelph.ca</t>
   </si>
   <si>
@@ -477,7 +480,10 @@
     <t>Campus Green</t>
   </si>
   <si>
-    <t>Fri Apr 04 02:11:32 EDT 2025</t>
+    <t>2025-04-14</t>
+  </si>
+  <si>
+    <t>, 100001, 100002</t>
   </si>
   <si>
     <t>AI Workshop</t>
@@ -492,6 +498,9 @@
     <t>Thornbrough 210</t>
   </si>
   <si>
+    <t>2025-04-24</t>
+  </si>
+  <si>
     <t>, 100001</t>
   </si>
   <si>
@@ -507,6 +516,9 @@
     <t>UC Courtyard</t>
   </si>
   <si>
+    <t>2025-03-18</t>
+  </si>
+  <si>
     <t>Event7</t>
   </si>
   <si>
@@ -516,6 +528,9 @@
     <t>UC</t>
   </si>
   <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
     <t>UC CLUB FAIR</t>
   </si>
   <si>
@@ -525,16 +540,13 @@
     <t>111</t>
   </si>
   <si>
-    <t>PROJECT DAY</t>
-  </si>
-  <si>
-    <t>CST100</t>
+    <t>2025-03-11</t>
   </si>
   <si>
     <t>Added via UI</t>
   </si>
   <si>
-    <t>THORN</t>
+    <t>2025-04-20</t>
   </si>
 </sst>
 </file>
@@ -579,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -628,14 +640,6 @@
       </c>
       <c r="B6" t="s" s="0">
         <v>11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -645,42 +649,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>0</v>
       </c>
       <c r="D1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="H1" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="I1" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="J1" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="K1" t="s" s="0">
         <v>21</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="K1" t="s" s="0">
-        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -688,25 +692,25 @@
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s" s="0">
         <v>25</v>
-      </c>
-      <c r="F2" t="n" s="0">
-        <v>50.0</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>27</v>
       </c>
       <c r="I2" t="n" s="0">
         <v>900.0</v>
@@ -715,7 +719,7 @@
         <v>1030.0</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -723,25 +727,25 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n" s="0">
         <v>40.0</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I3" t="n" s="0">
         <v>1100.0</v>
@@ -750,7 +754,7 @@
         <v>1230.0</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -758,25 +762,25 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>30.0</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I4" t="n" s="0">
         <v>1400.0</v>
@@ -785,7 +789,7 @@
         <v>1530.0</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -793,25 +797,25 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I5" t="n" s="0">
         <v>1140.0</v>
@@ -820,7 +824,7 @@
         <v>1500.0</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -828,25 +832,25 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>25.0</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I6" t="n" s="0">
         <v>1500.0</v>
@@ -855,7 +859,7 @@
         <v>1700.0</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -863,25 +867,25 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n" s="0">
         <v>50.0</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I7" t="n" s="0">
         <v>900.0</v>
@@ -890,7 +894,7 @@
         <v>1100.0</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -898,25 +902,25 @@
         <v>12.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n" s="0">
         <v>50.0</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I8" t="n" s="0">
         <v>1120.0</v>
@@ -925,7 +929,42 @@
         <v>1200.0</v>
       </c>
       <c r="K8" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="G9" t="s" s="0">
         <v>50</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>930.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>1200.0</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1305,7 +1344,7 @@
         <v>113</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>114</v>
@@ -1314,113 +1353,113 @@
         <v>115</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>114</v>
@@ -1429,13 +1468,13 @@
         <v>115</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1450,45 +1489,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F2" t="n" s="0">
         <v>100.0</v>
@@ -1497,24 +1536,24 @@
         <v>0.0</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>72</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F3" t="n" s="0">
         <v>30.0</v>
@@ -1523,24 +1562,24 @@
         <v>15.0</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>150.0</v>
@@ -1554,19 +1593,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>72</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="F5" t="n" s="0">
         <v>11.0</v>
@@ -1580,19 +1619,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>72</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>11.0</v>
@@ -1606,22 +1645,22 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="G7" t="n" s="0">
         <v>0.0</v>
@@ -1632,22 +1671,22 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="G8" t="n" s="0">
         <v>0.0</v>

--- a/src/UMS_Data.xlsx
+++ b/src/UMS_Data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="183">
   <si>
     <t>Subject Code</t>
   </si>
@@ -24,36 +24,36 @@
     <t>Subject Name</t>
   </si>
   <si>
+    <t>MATH001</t>
+  </si>
+  <si>
     <t>Mathematics</t>
   </si>
   <si>
-    <t>MATH001</t>
+    <t>CS201</t>
   </si>
   <si>
     <t>Computer Science</t>
   </si>
   <si>
-    <t>CS201</t>
+    <t>ENG101</t>
   </si>
   <si>
     <t>English</t>
   </si>
   <si>
-    <t>ENG101</t>
+    <t>PHY110</t>
   </si>
   <si>
     <t>Physics</t>
   </si>
   <si>
-    <t>PHY110</t>
+    <t>CHEM200</t>
   </si>
   <si>
     <t>Chemistry</t>
   </si>
   <si>
-    <t>CHEM200</t>
-  </si>
-  <si>
     <t>Course ID</t>
   </si>
   <si>
@@ -102,6 +102,9 @@
     <t>Object-Oriented Programming</t>
   </si>
   <si>
+    <t>Dr. Turing</t>
+  </si>
+  <si>
     <t>Room 202</t>
   </si>
   <si>
@@ -165,7 +168,7 @@
     <t>2025-04-09T00:00</t>
   </si>
   <si>
-    <t>MECHANICS</t>
+    <t>Mechanics</t>
   </si>
   <si>
     <t>THORN</t>
@@ -237,10 +240,10 @@
     <t/>
   </si>
   <si>
-    <t>Mathematics, Chemistry</t>
-  </si>
-  <si>
-    <t>1, 4, 5</t>
+    <t>MATH001, CHEM200</t>
+  </si>
+  <si>
+    <t>4, 5, 6, 1</t>
   </si>
   <si>
     <t>Barbra John</t>
@@ -264,84 +267,90 @@
     <t>AI Research</t>
   </si>
   <si>
-    <t>Computer Science, Mathematics</t>
+    <t>CS201, MATH001, CHEM200</t>
+  </si>
+  <si>
+    <t>5, 6, 1</t>
+  </si>
+  <si>
+    <t>Farhan Khan</t>
+  </si>
+  <si>
+    <t>farpass</t>
+  </si>
+  <si>
+    <t>789 Pine Rd</t>
+  </si>
+  <si>
+    <t>farhan@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>Winter 2025</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>ENG101, CHEM200, MATH001</t>
+  </si>
+  <si>
+    <t>3, 4, 1</t>
+  </si>
+  <si>
+    <t>Lucy Smith</t>
+  </si>
+  <si>
+    <t>lucypass</t>
+  </si>
+  <si>
+    <t>321 Birch St</t>
+  </si>
+  <si>
+    <t>lucy@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>MATH001, CS201</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Huzaifa</t>
+  </si>
+  <si>
+    <t>password123</t>
+  </si>
+  <si>
+    <t>428 Searles Court</t>
+  </si>
+  <si>
+    <t>anwar@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>Winter 2024</t>
+  </si>
+  <si>
+    <t>MATH001, CS201, ENG101</t>
+  </si>
+  <si>
+    <t>1, 2</t>
+  </si>
+  <si>
+    <t>Ayaan Ahmed</t>
+  </si>
+  <si>
+    <t>786 Steven Road</t>
+  </si>
+  <si>
+    <t>ayaanh@uoguelph.ca</t>
+  </si>
+  <si>
+    <t>PH.d</t>
   </si>
   <si>
     <t>2, 1</t>
   </si>
   <si>
-    <t>Farhan Khan</t>
-  </si>
-  <si>
-    <t>farpass</t>
-  </si>
-  <si>
-    <t>789 Pine Rd</t>
-  </si>
-  <si>
-    <t>farhan@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>Winter 2025</t>
-  </si>
-  <si>
-    <t>Data Science</t>
-  </si>
-  <si>
-    <t>English, Chemistry, Mathematics</t>
-  </si>
-  <si>
-    <t>3, 4, 1</t>
-  </si>
-  <si>
-    <t>Lucy Smith</t>
-  </si>
-  <si>
-    <t>lucypass</t>
-  </si>
-  <si>
-    <t>321 Birch St</t>
-  </si>
-  <si>
-    <t>lucy@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>Mathematics, Computer Science</t>
-  </si>
-  <si>
-    <t>1, 2</t>
-  </si>
-  <si>
-    <t>Huzaifa</t>
-  </si>
-  <si>
-    <t>password123</t>
-  </si>
-  <si>
-    <t>428 Searles Court</t>
-  </si>
-  <si>
-    <t>anwar@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>Winter 2024</t>
-  </si>
-  <si>
-    <t>Mathematics, Computer Science, English</t>
-  </si>
-  <si>
-    <t>Ayaan Ahmed</t>
-  </si>
-  <si>
-    <t>786 Steven Road</t>
-  </si>
-  <si>
-    <t>ayaanh@uoguelph.ca</t>
-  </si>
-  <si>
-    <t>PH.d</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -378,9 +387,6 @@
     <t>FAC002</t>
   </si>
   <si>
-    <t>Dr. Turing</t>
-  </si>
-  <si>
     <t>PhD in Computer Science</t>
   </si>
   <si>
@@ -477,76 +483,88 @@
     <t>Start-of-semester BBQ to welcome new students.</t>
   </si>
   <si>
+    <t>Library</t>
+  </si>
+  <si>
+    <t>2025-04-14</t>
+  </si>
+  <si>
+    <t>, 100001, 100002</t>
+  </si>
+  <si>
+    <t>AI Workshop</t>
+  </si>
+  <si>
+    <t>E002</t>
+  </si>
+  <si>
+    <t>Hands-on session on Artificial Intelligence.</t>
+  </si>
+  <si>
+    <t>Thornbrough 210</t>
+  </si>
+  <si>
+    <t>2025-04-24</t>
+  </si>
+  <si>
+    <t>, 100001</t>
+  </si>
+  <si>
+    <t>Career Fair</t>
+  </si>
+  <si>
+    <t>E003</t>
+  </si>
+  <si>
+    <t>Meet employers and get career advice.</t>
+  </si>
+  <si>
+    <t>UC Courtyard</t>
+  </si>
+  <si>
+    <t>2025-03-18</t>
+  </si>
+  <si>
+    <t>Event7</t>
+  </si>
+  <si>
+    <t>E007</t>
+  </si>
+  <si>
+    <t>Athletic Centre</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>, 100002, 100003</t>
+  </si>
+  <si>
+    <t>UC CLUB FAIR</t>
+  </si>
+  <si>
+    <t>UC90</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2025-03-11</t>
+  </si>
+  <si>
+    <t>Added via UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UC </t>
+  </si>
+  <si>
+    <t>2025-04-20</t>
+  </si>
+  <si>
     <t>Campus Green</t>
   </si>
   <si>
-    <t>2025-04-14</t>
-  </si>
-  <si>
-    <t>, 100001, 100002</t>
-  </si>
-  <si>
-    <t>AI Workshop</t>
-  </si>
-  <si>
-    <t>E002</t>
-  </si>
-  <si>
-    <t>Hands-on session on Artificial Intelligence.</t>
-  </si>
-  <si>
-    <t>Thornbrough 210</t>
-  </si>
-  <si>
-    <t>2025-04-24</t>
-  </si>
-  <si>
-    <t>, 100001</t>
-  </si>
-  <si>
-    <t>Career Fair</t>
-  </si>
-  <si>
-    <t>E003</t>
-  </si>
-  <si>
-    <t>Meet employers and get career advice.</t>
-  </si>
-  <si>
-    <t>UC Courtyard</t>
-  </si>
-  <si>
-    <t>2025-03-18</t>
-  </si>
-  <si>
-    <t>Event7</t>
-  </si>
-  <si>
-    <t>E007</t>
-  </si>
-  <si>
-    <t>UC</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>UC CLUB FAIR</t>
-  </si>
-  <si>
-    <t>UC90</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2025-03-11</t>
-  </si>
-  <si>
-    <t>Added via UI</t>
-  </si>
-  <si>
-    <t>2025-04-20</t>
+    <t>, 870003</t>
   </si>
 </sst>
 </file>
@@ -695,7 +713,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -730,22 +748,22 @@
         <v>27</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n" s="0">
         <v>40.0</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n" s="0">
         <v>1100.0</v>
@@ -754,7 +772,7 @@
         <v>1230.0</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -762,10 +780,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>1.0</v>
@@ -777,10 +795,10 @@
         <v>30.0</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I4" t="n" s="0">
         <v>1400.0</v>
@@ -789,7 +807,7 @@
         <v>1530.0</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -797,25 +815,25 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n" s="0">
         <v>1140.0</v>
@@ -824,7 +842,7 @@
         <v>1500.0</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -832,25 +850,25 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>25.0</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I6" t="n" s="0">
         <v>1500.0</v>
@@ -859,7 +877,7 @@
         <v>1700.0</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -867,25 +885,25 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" t="n" s="0">
         <v>50.0</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I7" t="n" s="0">
         <v>900.0</v>
@@ -894,7 +912,7 @@
         <v>1100.0</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -902,10 +920,10 @@
         <v>12.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>1.0</v>
@@ -917,10 +935,10 @@
         <v>50.0</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n" s="0">
         <v>1120.0</v>
@@ -929,7 +947,7 @@
         <v>1200.0</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -937,10 +955,10 @@
         <v>7.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>1.0</v>
@@ -949,10 +967,10 @@
         <v>23</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>50.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>25</v>
@@ -964,7 +982,7 @@
         <v>1200.0</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -979,49 +997,49 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2">
@@ -1029,13 +1047,13 @@
         <v>100001.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.23456789E9</v>
@@ -1047,28 +1065,28 @@
         <v>2000.0</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I2" t="n" s="0">
         <v>85.0</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M2" t="n" s="0">
         <v>-1.0</v>
       </c>
       <c r="N2" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O2" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -1076,13 +1094,13 @@
         <v>100002.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>9.87654321E8</v>
@@ -1094,28 +1112,28 @@
         <v>1000.0</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" t="n" s="0">
         <v>90.0</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M3" t="n" s="0">
         <v>-1.0</v>
       </c>
       <c r="N3" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O3" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -1123,13 +1141,13 @@
         <v>100003.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>5.55666777E8</v>
@@ -1141,28 +1159,28 @@
         <v>3000.0</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I4" t="n" s="0">
         <v>88.0</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M4" t="n" s="0">
         <v>-1.0</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
@@ -1170,13 +1188,13 @@
         <v>100004.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" t="n" s="0">
         <v>4.44555666E8</v>
@@ -1188,28 +1206,28 @@
         <v>2500.0</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I5" t="n" s="0">
         <v>75.0</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M5" t="n" s="0">
         <v>-1.0</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -1217,13 +1235,13 @@
         <v>870003.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>6.476748616E9</v>
@@ -1235,28 +1253,28 @@
         <v>0.0</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" t="n" s="0">
         <v>-1.0</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -1264,13 +1282,13 @@
         <v>901988.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7" t="n" s="0">
         <v>6.845789546E9</v>
@@ -1282,28 +1300,28 @@
         <v>0.0</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I7" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L7" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M7" t="n" s="0">
         <v>-1.0</v>
       </c>
       <c r="N7" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O7" t="s" s="0">
-        <v>83</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1318,163 +1336,163 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>23</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="E4" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="C4" t="s" s="0">
-        <v>127</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>128</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>35</v>
-      </c>
       <c r="F4" t="s" s="0">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>23</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1489,45 +1507,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F2" t="n" s="0">
         <v>100.0</v>
@@ -1536,24 +1554,24 @@
         <v>0.0</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F3" t="n" s="0">
         <v>30.0</v>
@@ -1562,24 +1580,24 @@
         <v>15.0</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>150.0</v>
@@ -1588,24 +1606,24 @@
         <v>0.0</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F5" t="n" s="0">
         <v>11.0</v>
@@ -1614,24 +1632,24 @@
         <v>11.0</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>72</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>11.0</v>
@@ -1640,24 +1658,24 @@
         <v>11.0</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F7" t="n" s="0">
         <v>100.0</v>
@@ -1666,24 +1684,24 @@
         <v>0.0</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>72</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F8" t="n" s="0">
         <v>100.0</v>
@@ -1692,7 +1710,7 @@
         <v>0.0</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>72</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
